--- a/macro/양식/애드로그메모_양식.xlsx
+++ b/macro/양식/애드로그메모_양식.xlsx
@@ -35,7 +35,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007B1FA2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000277BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,22 +465,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>변경조건</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>변경결과</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>삭제조건</t>
         </is>
